--- a/2. RECTIFICADOR TRIFASICO MEDIA ONDA NO CONTROLADO/datos_r3p_half_wave.xlsx
+++ b/2. RECTIFICADOR TRIFASICO MEDIA ONDA NO CONTROLADO/datos_r3p_half_wave.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bremdows\UNSAAC\SEMESTRE X\LABORATORIO DE SISTEMAS ELECTRONICOS DE POTENCIA\lab-sistemas-electronicos-potencia\2. RECTIFICAR TRIFASICO - MEDIA ONDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bremdows\UNSAAC\SEMESTRE X\LABORATORIO DE SISTEMAS ELECTRONICOS DE POTENCIA\lab-sistemas-electronicos-potencia\2. RECTIFICADOR TRIFASICO MEDIA ONDA NO CONTROLADO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18FC702C-E67E-4DC6-B00E-2CED3B570DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C45F0D-C177-4083-AB43-B510137FB946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="456" windowWidth="11520" windowHeight="12504" xr2:uid="{97B723EC-598A-465F-8F2E-C8FE302ECCE1}"/>
+    <workbookView xWindow="0" yWindow="456" windowWidth="11520" windowHeight="12504" xr2:uid="{97B723EC-598A-465F-8F2E-C8FE302ECCE1}"/>
   </bookViews>
   <sheets>
     <sheet name="R" sheetId="1" r:id="rId1"/>
@@ -574,6 +574,9 @@
       <c r="E10" t="s">
         <v>17</v>
       </c>
+      <c r="F10">
+        <v>117.5716</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
